--- a/data/trans_orig/P21D5_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psiquiatra) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>194584</t>
+          <t>194577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>216754</t>
+          <t>216735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>198588</t>
+          <t>199009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210777</t>
+          <t>210775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>400677</t>
+          <t>400170</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424218</t>
+          <t>424984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36133</t>
+          <t>36276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>154943</t>
+          <t>154723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172693</t>
+          <t>173103</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>158173</t>
+          <t>158466</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172281</t>
+          <t>172454</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>322006</t>
+          <t>321042</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>342868</t>
+          <t>342871</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22771</t>
+          <t>24254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>30858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>17876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,62 +1673,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3503</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56252</t>
+          <t>48242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>399157</t>
+          <t>401828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72132</t>
+          <t>72487</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77536</t>
+          <t>77836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91102</t>
+          <t>70071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475840</t>
+          <t>475715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>251824</t>
+          <t>251823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>358797</t>
+          <t>366224</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>402655</t>
+          <t>423339</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>412</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2512</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3196</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,62 +2242,62 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5966</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>423866</t>
+          <t>423291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>443095</t>
+          <t>442922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>311629</t>
+          <t>312516</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>325430</t>
+          <t>325771</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>742730</t>
+          <t>742186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>764489</t>
+          <t>765055</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23801</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44915</t>
+          <t>42989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>204130</t>
+          <t>204385</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>218165</t>
+          <t>218268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>381306</t>
+          <t>381823</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>401590</t>
+          <t>402718</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>591513</t>
+          <t>592363</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>615737</t>
+          <t>616400</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>26009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37597</t>
+          <t>37947</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8632</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>868</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113358</t>
+          <t>112743</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>122308</t>
+          <t>122326</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>290035</t>
+          <t>291042</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>306727</t>
+          <t>307053</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>407357</t>
+          <t>408236</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>426644</t>
+          <t>426681</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29704</t>
+          <t>29582</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3914,97 +3914,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>4140</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2871</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>581</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2939</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2943</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>773740</t>
+          <t>810958</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1543471</t>
+          <t>1544272</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1442074</t>
+          <t>1442847</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1478340</t>
+          <t>1477055</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2104368</t>
+          <t>2098997</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3005673</t>
+          <t>3008197</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>64181</t>
+          <t>63146</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>840972</t>
+          <t>802288</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>52029</t>
+          <t>52236</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>81292</t>
+          <t>80553</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>129184</t>
+          <t>126780</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1036815</t>
+          <t>1046057</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17881</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>37136</t>
+          <t>37231</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D5_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D5_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>209354</t>
+          <t>229029</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>194577</t>
+          <t>215812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>216735</t>
+          <t>236352</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>206182</t>
+          <t>222120</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>199009</t>
+          <t>213215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210775</t>
+          <t>227063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>415536</t>
+          <t>451148</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>400170</t>
+          <t>435927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424984</t>
+          <t>461094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11964</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27970</t>
+          <t>24144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36276</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>166149</t>
+          <t>181162</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>154723</t>
+          <t>170841</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173103</t>
+          <t>188019</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167788</t>
+          <t>185507</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>158466</t>
+          <t>177166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172454</t>
+          <t>190277</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>333936</t>
+          <t>366668</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>321042</t>
+          <t>353571</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>342871</t>
+          <t>375229</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18062</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>11961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30858</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15325</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>162368</t>
+          <t>178976</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48242</t>
+          <t>170621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>401828</t>
+          <t>184113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75774</t>
+          <t>83172</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72487</t>
+          <t>79255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77836</t>
+          <t>85455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>238142</t>
+          <t>262148</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70071</t>
+          <t>253372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475715</t>
+          <t>267979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>251823</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>366224</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>254589</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>423339</t>
+          <t>20317</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>432</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,27 +2432,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>434937</t>
+          <t>487834</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>423291</t>
+          <t>475661</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>442922</t>
+          <t>496159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>319591</t>
+          <t>364848</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>312516</t>
+          <t>356594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>325771</t>
+          <t>371327</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>754529</t>
+          <t>852682</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>742186</t>
+          <t>838030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>765055</t>
+          <t>863390</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>17973</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>29928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>26396</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>32770</t>
+          <t>36692</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>52025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>455845</t>
+          <t>510679</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>455845</t>
+          <t>510679</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>455845</t>
+          <t>510679</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>794602</t>
+          <t>897346</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>794602</t>
+          <t>897346</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>794602</t>
+          <t>897346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>213327</t>
+          <t>257216</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>204385</t>
+          <t>248849</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>218268</t>
+          <t>262291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>390819</t>
+          <t>360706</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>381823</t>
+          <t>352008</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>402718</t>
+          <t>368313</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>604145</t>
+          <t>617922</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>592363</t>
+          <t>606380</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>616400</t>
+          <t>626986</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>26720</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>38670</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7865</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,22 +3297,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>637956</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>637956</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>637956</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>119235</t>
+          <t>113090</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112743</t>
+          <t>106960</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>122326</t>
+          <t>116346</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>300604</t>
+          <t>335736</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>291042</t>
+          <t>324473</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>307053</t>
+          <t>342417</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>419840</t>
+          <t>448826</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>408236</t>
+          <t>436014</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>426681</t>
+          <t>457013</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23959</t>
+          <t>26166</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>18359</t>
+          <t>19791</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,22 +3866,22 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>611</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>611</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>354500</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>354500</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>354500</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>441450</t>
+          <t>471937</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>441450</t>
+          <t>471937</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>441450</t>
+          <t>471937</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1305369</t>
+          <t>1447306</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>810958</t>
+          <t>1423852</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1544272</t>
+          <t>1463981</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1460758</t>
+          <t>1552088</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1442847</t>
+          <t>1534940</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1477055</t>
+          <t>1567984</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2766128</t>
+          <t>2999395</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2098997</t>
+          <t>2971955</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3008197</t>
+          <t>3023458</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>304645</t>
+          <t>63434</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>48039</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>802288</t>
+          <t>84390</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,67 +4287,67 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>66965</t>
+          <t>73889</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>52236</t>
+          <t>60294</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>80553</t>
+          <t>89614</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>137324</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>115186</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>161755</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>371610</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>126780</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1046057</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>24650</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>24340</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>37231</t>
+          <t>36821</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>11949</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1623071</t>
+          <t>1524298</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1623071</t>
+          <t>1524298</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1623071</t>
+          <t>1524298</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1547675</t>
+          <t>1647114</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1547675</t>
+          <t>1647114</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1547675</t>
+          <t>1647114</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3170746</t>
+          <t>3171412</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3170746</t>
+          <t>3171412</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3170746</t>
+          <t>3171412</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
